--- a/artfynd/A 40355-2022 artfynd.xlsx
+++ b/artfynd/A 40355-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40355-2022 artfynd.xlsx
+++ b/artfynd/A 40355-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>462707</v>
+        <v>460664</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,26 +703,17 @@
           <t>Lam.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäcken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323536.9243699084</v>
+        <v>323537</v>
       </c>
       <c r="R2" t="n">
-        <v>6557745.296823381</v>
+        <v>6557745</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1926-06-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1926-06-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Vid uppfartsvägen på häll. Följeväxter: kungsmynta, hällebräken, kärleksört</t>
+          <t>Fältdagbok: 1926. Gunnar Johansson. Folkärna [Lohammar i Växtekologiska avdelningens arkiv, Uppsala universitet]: Nössemark. Bäcken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,11 +767,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bergäll</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -804,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Persson, Lars-Olof Persson</t>
+          <t>Via Dalsland Floraväktarna</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 40355-2022 artfynd.xlsx
+++ b/artfynd/A 40355-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,8 +788,16 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/460664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>